--- a/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4B491CE-8C95-4D4A-BCD3-3B3B3C48F615}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95718B43-B57F-47E2-AF4B-1B4C8FFFD1C1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBA55F73-F7E4-400B-836C-7A92D5D6775D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F49FD1A7-8B48-4B1C-BA65-896F4A76FCE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3AEF1F3-89DB-480F-AADB-E3373D05DCC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{023BD479-1131-4694-AF3E-DCD193BBB0F4}"/>
 </file>